--- a/artfynd/A 58129-2021 artfynd.xlsx
+++ b/artfynd/A 58129-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58129-2021 artfynd.xlsx
+++ b/artfynd/A 58129-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96471372</v>
+        <v>96471731</v>
       </c>
       <c r="B2" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>850200.5323169823</v>
+        <v>850177</v>
       </c>
       <c r="R2" t="n">
-        <v>7520990.139194387</v>
+        <v>7521114</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96471405</v>
+        <v>96471587</v>
       </c>
       <c r="B3" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>3242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>850170.195255592</v>
+        <v>850131</v>
       </c>
       <c r="R3" t="n">
-        <v>7521017.700586502</v>
+        <v>7521104</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96471423</v>
+        <v>96471372</v>
       </c>
       <c r="B4" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +882,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>850154.667153612</v>
+        <v>850200</v>
       </c>
       <c r="R4" t="n">
-        <v>7521061.519068722</v>
+        <v>7520990</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +940,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,37 +969,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96472483</v>
+        <v>96472467</v>
       </c>
       <c r="B5" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>850252.9112950242</v>
+        <v>850244</v>
       </c>
       <c r="R5" t="n">
-        <v>7521094.751743176</v>
+        <v>7521077</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1038,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96472182</v>
+        <v>96471423</v>
       </c>
       <c r="B6" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>850151.6216476375</v>
+        <v>850155</v>
       </c>
       <c r="R6" t="n">
-        <v>7521202.279227397</v>
+        <v>7521062</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1136,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96472467</v>
+        <v>96471685</v>
       </c>
       <c r="B7" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>850244.1485304316</v>
+        <v>850157</v>
       </c>
       <c r="R7" t="n">
-        <v>7521076.604876977</v>
+        <v>7521101</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,19 +1234,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,15 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96471587</v>
+        <v>96471780</v>
       </c>
       <c r="B8" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,21 +1274,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1299,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>850130.9479701302</v>
+        <v>850162</v>
       </c>
       <c r="R8" t="n">
-        <v>7521103.081361779</v>
+        <v>7521191</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,19 +1332,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,37 +1361,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96471685</v>
+        <v>96472483</v>
       </c>
       <c r="B9" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>850158.1572557258</v>
+        <v>850253</v>
       </c>
       <c r="R9" t="n">
-        <v>7521101.715566129</v>
+        <v>7521094</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1540,19 +1430,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,37 +1459,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96471731</v>
+        <v>96472489</v>
       </c>
       <c r="B10" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>850176.9882372294</v>
+        <v>850253</v>
       </c>
       <c r="R10" t="n">
-        <v>7521113.883505632</v>
+        <v>7521094</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,19 +1528,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,15 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96471309</v>
+        <v>96472182</v>
       </c>
       <c r="B11" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>850226.3509519796</v>
+        <v>850152</v>
       </c>
       <c r="R11" t="n">
-        <v>7520990.515836468</v>
+        <v>7521203</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1766,19 +1626,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,37 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96472489</v>
+        <v>96471309</v>
       </c>
       <c r="B12" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1846,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>850253.0637590587</v>
+        <v>850226</v>
       </c>
       <c r="R12" t="n">
-        <v>7521093.615045206</v>
+        <v>7520990</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,19 +1724,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,6 +1750,104 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>96471405</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Pajala, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>850169</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7521017</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58129-2021 artfynd.xlsx
+++ b/artfynd/A 58129-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96471731</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96471587</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96471372</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96472467</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96471423</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96471685</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96471780</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96472483</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96472489</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96472182</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1750,6 +1805,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96471309</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,8 +1908,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96471405</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>